--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 06/01. Báo giá bảo hành/BG_ThanhTamNhaTrang_200626.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 06/01. Báo giá bảo hành/BG_ThanhTamNhaTrang_200626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 06\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F262BD-76CA-4749-90D4-818C83AB7218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B964C566-1957-4648-B0AB-45B8B04752F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>006011074342924</t>
+  </si>
+  <si>
+    <t>Báo giá khạch không đồng ý sửa</t>
   </si>
 </sst>
 </file>
@@ -433,6 +436,84 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="13"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="13"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -463,6 +544,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -480,93 +570,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="13"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="13"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -949,135 +952,135 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="60" t="s">
+      <c r="A1" s="44"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="62"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="56"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="25" t="s">
+      <c r="A2" s="47"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="27"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="28" t="s">
+      <c r="A3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="30"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="31" t="s">
+      <c r="A4" s="49"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="33"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="36"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="40"/>
     </row>
     <row r="6" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
       <c r="J6" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47" t="s">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="48"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
       <c r="AA9" s="2"/>
     </row>
     <row r="10" spans="1:27" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1120,7 +1123,7 @@
       <c r="B11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="31" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -1148,17 +1151,17 @@
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="43"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="34"/>
       <c r="J12" s="17">
         <f>SUM(J11)</f>
         <v>200000</v>
@@ -1167,7 +1170,9 @@
     </row>
     <row r="13" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
+      <c r="B13" s="13" t="s">
+        <v>32</v>
+      </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
@@ -1179,148 +1184,148 @@
       <c r="AA13" s="2"/>
     </row>
     <row r="14" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="47"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="46"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="20"/>
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="50" t="s">
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
       <c r="E16" s="6"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="53"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="53"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="54"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47" t="s">
+      <c r="A19" s="27"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="G19" s="48"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="54"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
+      <c r="A20" s="27"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
       <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="54"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
       <c r="AA21" s="2"/>
     </row>
     <row r="22" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="55"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="55" t="s">
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="55"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
       <c r="K22" s="11"/>
       <c r="AA22" s="2"/>
     </row>
     <row r="23" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
       <c r="AA23" s="2"/>
     </row>
     <row r="24" spans="1:27" ht="17.25" x14ac:dyDescent="0.3">
@@ -1384,6 +1389,16 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="17">
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A15:D15"/>
@@ -1391,16 +1406,6 @@
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="G22:J22"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="D4:J4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
